--- a/experiment/HAT+CNN_bestx4/Test/results-Manga109/Manga109.xlsx
+++ b/experiment/HAT+CNN_bestx4/Test/results-Manga109/Manga109.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.37</v>
+        <v>28.38</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8183</v>
+        <v>0.8188</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8126</v>
+        <v>0.8127</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>28.21</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8448</v>
+        <v>0.8447</v>
       </c>
     </row>
     <row r="5">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.53</v>
+        <v>39.46</v>
       </c>
       <c r="C6" t="n">
-        <v>0.978</v>
+        <v>0.9778</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>30.05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9144</v>
+        <v>0.9141</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.22</v>
+        <v>33.31</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9567</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.14</v>
+        <v>27.13</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8933</v>
+        <v>0.8931</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>30.71</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9271</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.42</v>
+        <v>29.47</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8954</v>
       </c>
     </row>
     <row r="12">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29.6</v>
+        <v>29.58</v>
       </c>
       <c r="C12" t="n">
         <v>0.95</v>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.09</v>
+        <v>28.11</v>
       </c>
       <c r="C13" t="n">
         <v>0.8645</v>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33.34</v>
+        <v>33.31</v>
       </c>
       <c r="C14" t="n">
         <v>0.9608</v>
@@ -624,7 +624,7 @@
         <v>31.98</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9023</v>
+        <v>0.9022</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.73</v>
+        <v>28.82</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9165</v>
+        <v>0.9172</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.69</v>
+        <v>27.72</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9083</v>
+        <v>0.9084</v>
       </c>
     </row>
     <row r="18">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30.86</v>
+        <v>30.91</v>
       </c>
       <c r="C18" t="n">
         <v>0.9558</v>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34.39</v>
+        <v>34.37</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9764</v>
+        <v>0.9762999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30.77</v>
+        <v>30.79</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9009</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.89</v>
+        <v>32.86</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9759</v>
+        <v>0.9757</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9234</v>
+        <v>0.9229000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.05</v>
+        <v>32.03</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9334</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.2</v>
+        <v>30.21</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>36.85</v>
+        <v>36.84</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9715</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.18</v>
+        <v>29.21</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9569</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="27">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.09</v>
+        <v>31.11</v>
       </c>
       <c r="C27" t="n">
         <v>0.9395</v>
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38.41</v>
+        <v>38.48</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9781</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="29">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.43</v>
+        <v>31.44</v>
       </c>
       <c r="C29" t="n">
         <v>0.9307</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33.11</v>
+        <v>33.2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9585</v>
+        <v>0.9587</v>
       </c>
     </row>
     <row r="31">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.3</v>
+        <v>31.31</v>
       </c>
       <c r="C31" t="n">
         <v>0.9413</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26.67</v>
+        <v>26.71</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9376</v>
+        <v>0.9379</v>
       </c>
     </row>
     <row r="33">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27.51</v>
+        <v>27.49</v>
       </c>
       <c r="C33" t="n">
         <v>0.9281</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.53</v>
+        <v>32.54</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8929</v>
+        <v>0.8933</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.54</v>
+        <v>28.56</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7417</v>
+        <v>0.7421</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26.37</v>
+        <v>26.36</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8689</v>
+        <v>0.8688</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9109</v>
+        <v>0.911</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.59</v>
+        <v>27.62</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8625</v>
+        <v>0.8628</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35.19</v>
+        <v>35.17</v>
       </c>
       <c r="C39" t="n">
-        <v>0.971</v>
+        <v>0.9707</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>34.76</v>
+        <v>34.74</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9617</v>
+        <v>0.9618</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         <v>28.12</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8979</v>
+        <v>0.8978</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30.86</v>
+        <v>30.85</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8675</v>
+        <v>0.8672</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32.73</v>
+        <v>32.79</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9151</v>
+        <v>0.9154</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         <v>20.8</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7418</v>
+        <v>0.7423999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.99</v>
+        <v>34.96</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9761</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25.04</v>
+        <v>25.02</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9186</v>
+        <v>0.9182</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27.56</v>
+        <v>27.58</v>
       </c>
       <c r="C47" t="n">
-        <v>0.897</v>
+        <v>0.8974</v>
       </c>
     </row>
     <row r="48">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>34.6</v>
+        <v>34.62</v>
       </c>
       <c r="C48" t="n">
         <v>0.9520999999999999</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26.84</v>
+        <v>26.83</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8657</v>
+        <v>0.8656</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.77</v>
+        <v>28.79</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9177</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26.62</v>
+        <v>26.63</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7598</v>
+        <v>0.7601</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.31</v>
+        <v>30.29</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9463</v>
+        <v>0.9461000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>33.11</v>
+        <v>33.14</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9443</v>
+        <v>0.9444</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>36.35</v>
+        <v>36.33</v>
       </c>
       <c r="C54" t="n">
-        <v>0.904</v>
+        <v>0.9038</v>
       </c>
     </row>
     <row r="55">
@@ -1144,7 +1144,7 @@
         <v>35.54</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9624</v>
+        <v>0.9623</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22.52</v>
+        <v>22.53</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7169</v>
+        <v>0.7175</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>33.04</v>
+        <v>33.06</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9663</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30.41</v>
+        <v>30.36</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9462</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9434</v>
+        <v>0.9435</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         <v>23.66</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7594</v>
+        <v>0.7593</v>
       </c>
     </row>
     <row r="61">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>33.34</v>
+        <v>33.36</v>
       </c>
       <c r="C61" t="n">
         <v>0.9701</v>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.78</v>
+        <v>31.8</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9466</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.71</v>
+        <v>30.77</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9484</v>
+        <v>0.9486</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.03</v>
+        <v>35.07</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9669</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>33.94</v>
+        <v>33.96</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9267</v>
+        <v>0.9266</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.15</v>
+        <v>25.13</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9298</v>
+        <v>0.9292</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32.05</v>
+        <v>32.01</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9392</v>
+        <v>0.9388</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>32.99</v>
+        <v>33.07</v>
       </c>
       <c r="C68" t="n">
-        <v>0.931</v>
+        <v>0.9315</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31.61</v>
+        <v>31.67</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9399</v>
+        <v>0.9401</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>28.25</v>
+        <v>28.27</v>
       </c>
       <c r="C70" t="n">
-        <v>0.921</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>30.95</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9374</v>
+        <v>0.9373</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27.87</v>
+        <v>27.88</v>
       </c>
       <c r="C72" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7114</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         <v>34.8</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9584</v>
+        <v>0.9583</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>33.8</v>
+        <v>33.84</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9503</v>
+        <v>0.9505</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28.01</v>
+        <v>28.02</v>
       </c>
       <c r="C75" t="n">
-        <v>0.888</v>
+        <v>0.8883</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         <v>29.59</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9</v>
+        <v>0.8999</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.32</v>
+        <v>30.33</v>
       </c>
       <c r="C77" t="n">
-        <v>0.931</v>
+        <v>0.9311</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>30.2</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8803</v>
+        <v>0.8802</v>
       </c>
     </row>
     <row r="79">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>31.02</v>
+        <v>30.99</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9339</v>
+        <v>0.9335</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>30.85</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9388</v>
+        <v>0.9386</v>
       </c>
     </row>
     <row r="82">
@@ -1508,7 +1508,7 @@
         <v>31.87</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.9026</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>31.39</v>
+        <v>31.44</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9594</v>
+        <v>0.9595</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27.53</v>
+        <v>27.56</v>
       </c>
       <c r="C85" t="n">
-        <v>0.944</v>
+        <v>0.9442</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9305</v>
+        <v>0.9304</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>28.47</v>
+        <v>28.48</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8741</v>
+        <v>0.8742</v>
       </c>
     </row>
     <row r="88">
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35.52</v>
+        <v>35.53</v>
       </c>
       <c r="C88" t="n">
         <v>0.9518</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>33.84</v>
+        <v>33.87</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9624</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>30.25</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9224</v>
+        <v>0.9223</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.21</v>
+        <v>25.23</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8596</v>
+        <v>0.8598</v>
       </c>
     </row>
     <row r="92">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>28.52</v>
+        <v>28.53</v>
       </c>
       <c r="C92" t="n">
         <v>0.9072</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27.32</v>
+        <v>27.31</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9479</v>
+        <v>0.9478</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>20.95</v>
+        <v>20.94</v>
       </c>
       <c r="C94" t="n">
-        <v>0.7349</v>
+        <v>0.7348</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>34.01</v>
+        <v>33.98</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9546</v>
+        <v>0.9543</v>
       </c>
     </row>
     <row r="96">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.59</v>
+        <v>26.58</v>
       </c>
       <c r="C96" t="n">
         <v>0.8818</v>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>29.45</v>
+        <v>29.49</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9048</v>
+        <v>0.9046999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>28.68</v>
+        <v>28.73</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9631</v>
+        <v>0.9631999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.96</v>
+        <v>25.95</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7617</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1742,7 @@
         <v>23.58</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8898</v>
+        <v>0.8897</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.21</v>
+        <v>27.2</v>
       </c>
       <c r="C102" t="n">
-        <v>0.9004</v>
+        <v>0.9003</v>
       </c>
     </row>
     <row r="103">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>23.33</v>
+        <v>23.19</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8358</v>
+        <v>0.8342000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>36.91</v>
+        <v>36.94</v>
       </c>
       <c r="C104" t="n">
         <v>0.9762</v>
@@ -1794,7 +1794,7 @@
         <v>28.79</v>
       </c>
       <c r="C105" t="n">
-        <v>0.9066</v>
+        <v>0.9067</v>
       </c>
     </row>
     <row r="106">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>33.11</v>
+        <v>33.04</v>
       </c>
       <c r="C106" t="n">
-        <v>0.9747</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>29.58</v>
+        <v>29.59</v>
       </c>
       <c r="C107" t="n">
-        <v>0.8871</v>
+        <v>0.8872</v>
       </c>
     </row>
     <row r="108">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>36.32</v>
+        <v>36.43</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9368</v>
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>31.5</v>
+        <v>31.49</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8609</v>
+        <v>0.8605</v>
       </c>
     </row>
     <row r="110">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28.55</v>
+        <v>28.6</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9131</v>
+        <v>0.9143</v>
       </c>
     </row>
     <row r="111">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>30.47</v>
+        <v>30.48</v>
       </c>
       <c r="C111" t="n">
         <v>0.9089</v>
